--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2857142857142857</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="C2">
-        <v>0.3333333333333333</v>
+        <v>0.5886524822695035</v>
       </c>
       <c r="D2">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7466666666666667</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="B2">
-        <v>0.04878048780487805</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C2">
-        <v>0.5886524822695035</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E2">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
